--- a/outputs/tables/appendix_c_between_country_variance.xlsx
+++ b/outputs/tables/appendix_c_between_country_variance.xlsx
@@ -442,10 +442,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.242</v>
+        <v>0.295</v>
       </c>
       <c r="C2" t="n">
-        <v>0.278</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="3">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.214</v>
+        <v>0.217</v>
       </c>
       <c r="C3" t="n">
-        <v>0.212</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="4">
@@ -468,35 +468,35 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.143</v>
+        <v>0.183</v>
       </c>
       <c r="C4" t="n">
-        <v>0.143</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Log loans</t>
+          <t>Leverage (assets/equity)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>0.145</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.145</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Leverage (assets/equity)</t>
+          <t>Log loans</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.118</v>
-      </c>
+        <v>0.133</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -505,36 +505,36 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.082</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.083</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Customer deposits</t>
+          <t>Gross loans &amp; advances</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.067</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gross loans &amp; advances</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="10">
@@ -544,75 +544,75 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.065</v>
+        <v>0.055</v>
       </c>
       <c r="C10" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Operating income</t>
+          <t>ROE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="C11" t="n">
-        <v>0.049</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Net interest income</t>
+          <t>ROA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="C12" t="n">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Equity ratio</t>
+          <t>Operating income</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.042</v>
+        <v>0.05</v>
       </c>
       <c r="C13" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ROA</t>
+          <t>Net interest income</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ROE</t>
+          <t>Equity ratio</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.036</v>
+        <v>0.043</v>
       </c>
       <c r="C15" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="16">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="C16" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="17">
@@ -636,7 +636,7 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.049</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="18">
@@ -647,7 +647,7 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0.155</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="19">
@@ -658,7 +658,7 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.196</v>
+        <v>0.203</v>
       </c>
     </row>
   </sheetData>
@@ -712,10 +712,10 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="D2" t="n">
-        <v>0.242</v>
+        <v>0.295</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0.067</v>
       </c>
       <c r="D3" t="n">
-        <v>0.278</v>
+        <v>0.295</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.896</v>
+        <v>0.894</v>
       </c>
       <c r="C2" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
